--- a/results/job_matches_2026-10-13.xlsx
+++ b/results/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,17 +596,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applications Development Programmer Analyst I</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tucson, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,42 +614,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
+          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Applications Development Programmer Analyst I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>University of Arizona</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Tucson, AZ, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
+          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
+          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Center - Memphis</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,67 +764,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ef5abedca53bda</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Data Product Owner</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0799847319eb195f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mid Software Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd94caafa09b4992</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Software Engineer, Data Center - Memphis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Colorado Springs, CO, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+          <t>https://www.indeed.com/viewjob?jk=0799847319eb195f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Infrastructure Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
+          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Mid Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Colorado Springs, CO, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
+          <t>https://www.indeed.com/viewjob?jk=cd94caafa09b4992</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, USA USA</t>
+          <t>NY, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea48901cd5b935f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4a15665a910f8e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,67 +1114,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46b78de53b33b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Cloud Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MetLife Legal Plans</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Round Rock, TX, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d843a20197d70</t>
+          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a8b6c2048e3a3a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dfe72a31f423d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d46b78de53b33b7b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>MetLife Legal Plans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carmel, IN, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
+          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
+          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8d843a20197d70</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data &amp; AI Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dfe72a31f423d4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Developer, Full Stack</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a8b6c2048e3a3a4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ArcGIS Enterprise</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redlands, CA, USA USA</t>
+          <t>Carmel, IN, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
+          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Software Developer, Senior</t>
+          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Advisor_BCDA1J</t>
+          <t>Python- AI Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bdadf1084f2459</t>
+          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data &amp; AI Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Report Developer II</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University Hospitals</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shaker Heights, OH, USA USA</t>
+          <t>Lehi, UT, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,42 +1559,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer, Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Northramp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>IT Software Developer, Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Software Development Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Redlands, CA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,67 +1674,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
+          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer- Full Stack</t>
+          <t>Report Developer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>University Hospitals</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, USA USA</t>
+          <t>Shaker Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
+          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Management and Database Administration Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Edison, NJ, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
+          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analyst, Business Intelligence &amp; Data Engineering</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f559355e662e5e19</t>
+          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer Engineer in Testing</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EBS-MINDS IT</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>DevOps Engineer, Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,137 +1884,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
+          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake dbt Developer</t>
+          <t>Software Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Victaulic</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VA, USA USA</t>
+          <t>Indianapolis, IN, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
+          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Management and Database Administration Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Round Rock, TX, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
+          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java)</t>
+          <t>Analyst, Business Intelligence &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brea, CA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
+          <t>https://www.indeed.com/viewjob?jk=f559355e662e5e19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EBS-MINDS IT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67fbdcf58161d238</t>
+          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Analyst</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Unity Catalog, BigQuery, Spark, PySpark, Snowflake, Star Schema, Power BI</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Knowledge Graph / Data Integration Engineer</t>
+          <t>Snowflake dbt Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OtterSoft</t>
+          <t>Victaulic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>VA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,67 +2094,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bitful Consulting</t>
+          <t>Shield Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wadsworth, OH, USA USA</t>
+          <t>Valencia, CA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
+          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e623558d354d72</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Consultant, Data Engineer (Databricks Experience)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Data Modeling, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,67 +2164,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655acdb6ab526044</t>
+          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer II (Java)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plymouth, MN, USA USA</t>
+          <t>Brea, CA, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bc7581ab37aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chantilly, VA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a9db3524607bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=67fbdcf58161d238</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate AWS DevOps Engineer</t>
+          <t>Senior Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, Databricks, Unity Catalog, BigQuery, Spark, PySpark, Snowflake, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075accddbedd75ac</t>
+          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OneKey MLS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Farmingdale, NY, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
+          <t>https://www.indeed.com/viewjob?jk=75651bec84129cee</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Data Engineer (Two Positions), P3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,34 +2329,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
+          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>Bitful Consulting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, VA, USA USA</t>
+          <t>Wadsworth, OH, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=63e623558d354d72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Knowledge Graph / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>OtterSoft</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d017d057e53ce8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+          <t>Senior Consultant, Data Engineer (Databricks Experience)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Data Modeling, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b19b6f1b88b438</t>
+          <t>https://www.indeed.com/viewjob?jk=655acdb6ab526044</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWM Technology</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Plymouth, MN, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
+          <t>https://www.indeed.com/viewjob?jk=90bc7581ab37aef8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | Contract | Remote</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tech Holding</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Chantilly, VA, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,34 +2504,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+          <t>https://www.indeed.com/viewjob?jk=26a9db3524607bc0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, S3 storage</t>
+          <t>Associate AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fremont, CA, USA USA</t>
+          <t>Sioux Falls, SD, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,34 +2539,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
+          <t>https://www.indeed.com/viewjob?jk=075accddbedd75ac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bitful Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,34 +2574,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d163842bf5835bf</t>
+          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer</t>
+          <t>Sr. Site Reliability Engineer, S3 storage</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, USA USA</t>
+          <t>Fremont, CA, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MySQL, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd53bc295db27f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,15 +2644,260 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Arlington, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d017d057e53ce8b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Siemens Healthineers</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Malvern, PA, USA USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b19b6f1b88b438</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AWM Technology</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, USA USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer | Contract | Remote</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tech Holding</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dallas, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, MySQL, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fd53bc295db27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Trinzic</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, USA USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6fe15f3fd01de120</t>
         </is>

--- a/results/job_matches_2026-10-13.xlsx
+++ b/results/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,70 +456,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Databricks Platform Engineer (Remote US)</t>
+          <t>IT Consultant - Cloud Specialist L2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Hanover, NJ, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=567f4ddfd333af1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALLISTOFUSION</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef0def19f3a7249</t>
+          <t>https://www.indeed.com/viewjob?jk=b6517d29fbe4469e</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Ops/AI Engineer (US Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Strongsville, OH, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,42 +579,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194ae6ae0e83b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=69e8721900a835a2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Systems Engineer, Data Management - East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
+          <t>https://www.indeed.com/viewjob?jk=31d93ef09b2d5ada</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications Development Programmer Analyst I</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tucson, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,34 +649,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
+          <t>https://www.indeed.com/viewjob?jk=e3693c9cd5da878e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Development Programmer Analyst I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>University of Arizona</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Tucson, AZ, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,77 +684,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
+          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>McGuireWoods LLP</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ef5abedca53bda</t>
+          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>US- Java Engineer - Pricing</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MoneyGram</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,67 +799,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb043241f1ba4c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Product Owner</t>
+          <t>Analytics Platform Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
+          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
+          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Center - Memphis</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Charlottesville, VA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,172 +904,172 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7130fbafa2f19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0799847319eb195f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>UKG Integration Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mid Software Engineer</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd94caafa09b4992</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Software Engineer, Data Center - Memphis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NY, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,59 +1079,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4a15665a910f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Infrastructure Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
+          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>NY, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,34 +1174,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4a15665a910f8e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Kennesaw, GA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,34 +1209,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,77 +1244,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46b78de53b33b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Cloud Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MetLife Legal Plans</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Round Rock, TX, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,67 +1324,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d843a20197d70</t>
+          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>.Net Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dfe72a31f423d4</t>
+          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a8b6c2048e3a3a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d46b78de53b33b7b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carmel, IN, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,67 +1429,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Python- AI Software Engineer III</t>
+          <t>Applications Administrator IV (IT Systems)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilmington, DE, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data &amp; AI Analyst</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>MetLife Legal Plans</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
+          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lehi, UT, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a8b6c2048e3a3a4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Developer, Full Stack</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Carmel, IN, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT Software Developer, Senior</t>
+          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ArcGIS Enterprise</t>
+          <t>Python- AI Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redlands, CA, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
+          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Report Developer II</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University Hospitals</t>
+          <t>Solero Workforce Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shaker Heights, OH, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data &amp; AI Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,67 +1744,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Lehi, UT, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Developer, Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Northramp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
+          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>IT Software Developer, Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,164 +1849,164 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
+          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Platform</t>
+          <t>Software Development Engineer II - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Redlands, CA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
+          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer- Full Stack</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
+          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Management and Database Administration Specialist</t>
+          <t>Report Developer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>University Hospitals</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Shaker Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analyst, Business Intelligence &amp; Data Engineering</t>
+          <t>Security Engineer (Application Security)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f559355e662e5e19</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer Engineer in Testing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EBS-MINDS IT</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Edison, NJ, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,102 +2024,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
+          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Snowflake dbt Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Victaulic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>DevOps Engineer, Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shield Healthcare</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valencia, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,67 +2129,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
+          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Indianapolis, IN, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java)</t>
+          <t>Data Management and Database Administration Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brea, CA, USA USA</t>
+          <t>Round Rock, TX, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
+          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EBS-MINDS IT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67fbdcf58161d238</t>
+          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Analyst</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,42 +2259,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Unity Catalog, BigQuery, Spark, PySpark, Snowflake, Star Schema, Power BI</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OneKey MLS</t>
+          <t>Shield Healthcare</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Farmingdale, NY, USA USA</t>
+          <t>Valencia, CA, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75651bec84129cee</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Two Positions), P3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bitful Consulting</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wadsworth, OH, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,94 +2374,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e623558d354d72</t>
+          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Knowledge Graph / Data Integration Engineer</t>
+          <t>Software Engineer II (Java)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OtterSoft</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Brea, CA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
+          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Consultant, Data Engineer (Databricks Experience)</t>
+          <t>Service Delivery Center, Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Data Modeling, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655acdb6ab526044</t>
+          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer (Two Positions), P3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plymouth, MN, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bc7581ab37aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Knowledge Graph / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>OtterSoft</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chantilly, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a9db3524607bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate AWS DevOps Engineer</t>
+          <t>Senior Consultant, Data Engineer (Databricks Experience)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Data Modeling, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075accddbedd75ac</t>
+          <t>https://www.indeed.com/viewjob?jk=655acdb6ab526044</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, S3 storage</t>
+          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fremont, CA, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
+          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Sr. Site Reliability Engineer, S3 storage</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Fremont, CA, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,34 +2644,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>All IT Solutions LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Arlington, VA, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d017d057e53ce8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b19b6f1b88b438</t>
+          <t>https://www.indeed.com/viewjob?jk=d017d057e53ce8b1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWM Technology</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
+          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | Contract | Remote</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare-Remote within the US</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tech Holding</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+          <t>https://www.indeed.com/viewjob?jk=41d006ba3e7f262a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer</t>
+          <t>Software Engineer III - AWM Technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MySQL, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd53bc295db27f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Web Site Developer Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trinzic</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,17 +2889,87 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe15f3fd01de120</t>
+          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer | Contract | Remote</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tech Holding</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Dallas, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sr Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Equiniti</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Woburn, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c4b84101d3572ca</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-13.xlsx
+++ b/results/job_matches_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT Consultant - Cloud Specialist L2</t>
+          <t>Systems Architect - TS/SCI w/ Poly required</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hanover, NJ, USA USA</t>
+          <t>Warrenton, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
+          <t>https://www.indeed.com/viewjob?jk=51b2560066a45e46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>IT Consultant - Cloud Specialist L2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Hanover, NJ, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,42 +519,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6517d29fbe4469e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c5b1d05ad98c56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9e8fec032270fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications Development Programmer Analyst I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tucson, AZ, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,42 +684,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
+          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87fe4de2e714f22</t>
+          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>Full-Stack Senior Developers</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Natoli Engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Saint Charles, MO, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer - Senior Associate</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
+          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Platform Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,42 +859,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
+          <t>https://www.indeed.com/viewjob?jk=e213d5c6c5856442</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer Senior Consultant I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McGuireWoods LLP</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7130fbafa2f19</t>
+          <t>https://www.indeed.com/viewjob?jk=e045cc6a43c6b4be</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,19 +939,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
+          <t>https://www.indeed.com/viewjob?jk=d106c1338953198c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UKG Integration Developer</t>
+          <t>DevOps / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>Alchemy Cloud</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, GCP, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US- Java Engineer - Pricing</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MoneyGram</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Adelphi, MD, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,67 +1009,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
+          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Charlottesville, VA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7130fbafa2f19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Center - Memphis</t>
+          <t>Senior Health Data Modeler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
+          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,67 +1114,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
+          <t>https://www.indeed.com/viewjob?jk=5c476b35c41be97e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
+          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NY, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4a15665a910f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=166247ae6ba80226</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>McGuireWoods LLP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=493059cbcfb9f04e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,102 +1254,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
+          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Infrastructure Engineer</t>
+          <t>UKG Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd00894ae3ccf24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I – SRE</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9eb4c3615ab029</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>.Net Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,102 +1359,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
+          <t>https://www.indeed.com/viewjob?jk=a595a72e3d3f9968</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. Support &amp; Post-Release Quality Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46b78de53b33b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=5898f422bfe5208e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Engineer Data II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d247a00ef97cfce</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Applications Administrator IV (IT Systems)</t>
+          <t>Software Engineer, Data Center - Memphis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8c11dc2598a352</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MetLife Legal Plans</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,137 +1534,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2de87a09b47cb83</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Engineer - PostgreSQL and MongoDB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a8b6c2048e3a3a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0c3e70a1257e99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Jr. Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carmel, IN, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Kennesaw, GA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python- AI Software Engineer III</t>
+          <t>.Net Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wilmington, DE, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=dded0af6d2070543</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Applications Administrator IV (IT Systems)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Solero Workforce Solutions</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,67 +1709,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1dc43bf4f44c94</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data &amp; AI Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Vertex AI, Scala, Snowflake, Data Modeling, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae65d4effd1829d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>o3 Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lehi, UT, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea8f0126c1468fe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Developer, Full Stack</t>
+          <t>Marketing Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>La Mirada, CA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT Software Developer, Senior</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Center Valley, PA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,34 +1839,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Kafka, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=41844b46aff0cb0b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ArcGIS Enterprise</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>MetLife Legal Plans</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redlands, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
+          <t>https://www.indeed.com/viewjob?jk=34d9c1df3e95561d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Python- AI Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, ECS, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9658475685b5c8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c5aa4a9fbcd4b6c3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Report Developer II</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University Hospitals</t>
+          <t>Solero Workforce Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shaker Heights, OH, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,29 +1944,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2830c33b549b2199</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Security Engineer (Application Security)</t>
+          <t>Senior Databrick Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>SDG Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,94 +1989,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d7a111fdf4824</t>
+          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Lehi, UT, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=527fb8088c169f3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Senior Software Applications Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2b4867303bf280</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
+          <t>https://www.indeed.com/viewjob?jk=108442bf9c7995d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb2022242ed43e7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer- Full Stack</t>
+          <t>DevOps Engineer, Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
+          <t>https://www.indeed.com/viewjob?jk=9968e46f0d946d92</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Management and Database Administration Specialist</t>
+          <t>Software Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Round Rock, TX, USA USA</t>
+          <t>Indianapolis, IN, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f73e4e18af54b50</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer Engineer in Testing</t>
+          <t>Senior Software Engineer - DevOps (Plex)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EBS-MINDS IT</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Mayfield Heights, OH, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,42 +2224,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8cadc6544ff917</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Data Management and Database Administration Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SpaceXSI</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>Round Rock, TX, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
+          <t>https://www.indeed.com/viewjob?jk=edd012e70e61ef0f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shield Healthcare</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valencia, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>SpaceXSI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1e101eb8b6e88c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Shield Healthcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Valencia, CA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
+          <t>EMR, RDS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb7ae63ee72e66e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brea, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
+          <t>https://www.indeed.com/viewjob?jk=a034f20a9a1e8675</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,137 +2444,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
+          <t>https://www.indeed.com/viewjob?jk=78a08ffb456de840</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (Two Positions), P3</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Databricks, Medallion Architecture, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8791571b665c9efc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Knowledge Graph / Data Integration Engineer</t>
+          <t>Senior Development Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OtterSoft</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
+          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Consultant, Data Engineer (Databricks Experience)</t>
+          <t>Software Engineer II (Java)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Brea, CA, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Data Modeling, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655acdb6ab526044</t>
+          <t>https://www.indeed.com/viewjob?jk=a8bea343d8b29a94</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Service Delivery Center, Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
+          <t>https://www.indeed.com/viewjob?jk=b8889c03578c4693</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
+          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Warren, MI, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
+          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, S3 storage</t>
+          <t>Senior Data Engineer IS - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fremont, CA, USA USA</t>
+          <t>WA, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
+          <t>https://www.indeed.com/viewjob?jk=077367514f0c7f89</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Data Engineer (Two Positions), P3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,34 +2679,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ETL, ELT, dbt, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961fb3a3a8b251f6</t>
+          <t>https://www.indeed.com/viewjob?jk=94213dc00fbf6a3a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,34 +2714,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b077b090cd4d1ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III, Data Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d017d057e53ce8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Databricks Platform Engineer / AI-MLOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>EAPPS TECH LLC dba Magicforce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf9bfd089ca9e4c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare-Remote within the US</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d006ba3e7f262a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ba22ee549c1229</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWM Technology</t>
+          <t>Senior Data Engineer IS - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Plainview, TX, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, NoSQL, DataOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0361db4f39d8edb9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Web Site Developer Engineer</t>
+          <t>Senior Full Stack Software Development Engineer - (React, GCP, Node, Angular)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, CI/CD, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b7bf97bf3d08af</t>
+          <t>https://www.indeed.com/viewjob?jk=31743146b6a0d95d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | Contract | Remote</t>
+          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tech Holding</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Hopkins, MN, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Sr. Site Reliability Engineer, S3 storage</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Equiniti</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Woburn, MA, USA USA</t>
+          <t>Fremont, CA, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,15 +2959,190 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Spark, Splunk, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcdf69eb1ba1e50c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Strategic Operational Solutions</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Washington, DC, USA USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1293dae16bacfe7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Localize</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Scala, Snowflake, MongoDB, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64a275f552b9e37f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Siemens Healthineers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Malvern, PA, USA USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef875202e4d9683</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer | Contract | Remote</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tech Holding</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dallas, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=374435df20714c48</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sr Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Equiniti</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Woburn, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4c4b84101d3572ca</t>
         </is>
